--- a/documents/EPREUVE_E5_TABLEAU_DE_SYNTHESE_-_BTS_SIO_2026.xlsx
+++ b/documents/EPREUVE_E5_TABLEAU_DE_SYNTHESE_-_BTS_SIO_2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerem\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PorteFolio\PorteFolio\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF108A9B-4CDF-4EE4-8342-59BB01C77BC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AFB0827-1262-4A29-B212-E3256110AE74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="50">
   <si>
     <t>Gérer le patrimoine informatique</t>
   </si>
@@ -739,9 +739,48 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -764,45 +803,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1246,56 +1246,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="24"/>
+      <c r="H1" s="26"/>
     </row>
     <row r="2" spans="1:43" ht="41.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
     </row>
     <row r="3" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="31" t="s">
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="26"/>
-      <c r="H3" s="32"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="45"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="30"/>
+      <c r="B4" s="42"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="43"/>
       <c r="F4" s="12" t="s">
         <v>8</v>
       </c>
@@ -1307,22 +1307,22 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="43" t="s">
+      <c r="A5" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="45"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="37"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="33" t="s">
+      <c r="A6" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="41" t="s">
+      <c r="B6" s="33" t="s">
         <v>19</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1345,8 +1345,8 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="325" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="34"/>
-      <c r="B7" s="42"/>
+      <c r="A7" s="25"/>
+      <c r="B7" s="34"/>
       <c r="C7" s="20" t="s">
         <v>9</v>
       </c>
@@ -1402,16 +1402,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="17.600000000000001" x14ac:dyDescent="0.3">
-      <c r="A8" s="35" t="s">
+      <c r="A8" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="36"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="37"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="29"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1696,7 +1696,9 @@
       <c r="D13" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="15"/>
+      <c r="E13" s="14" t="s">
+        <v>37</v>
+      </c>
       <c r="F13" s="14" t="s">
         <v>37</v>
       </c>
@@ -1968,16 +1970,16 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="17.600000000000001" x14ac:dyDescent="0.3">
-      <c r="A19" s="38" t="s">
+      <c r="A19" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="39"/>
-      <c r="C19" s="39"/>
-      <c r="D19" s="39"/>
-      <c r="E19" s="39"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="39"/>
-      <c r="H19" s="40"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="31"/>
+      <c r="H19" s="32"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -2362,16 +2364,16 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="17.600000000000001" x14ac:dyDescent="0.3">
-      <c r="A27" s="38" t="s">
+      <c r="A27" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="B27" s="39"/>
-      <c r="C27" s="39"/>
-      <c r="D27" s="39"/>
-      <c r="E27" s="39"/>
-      <c r="F27" s="39"/>
-      <c r="G27" s="39"/>
-      <c r="H27" s="40"/>
+      <c r="B27" s="31"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="31"/>
+      <c r="G27" s="31"/>
+      <c r="H27" s="32"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2418,7 +2420,9 @@
       <c r="C28" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D28" s="15"/>
+      <c r="D28" s="8" t="s">
+        <v>35</v>
+      </c>
       <c r="E28" s="21"/>
       <c r="F28" s="21" t="s">
         <v>30</v>
@@ -2828,6 +2832,11 @@
     <row r="81" customFormat="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2835,11 +2844,6 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/documents/EPREUVE_E5_TABLEAU_DE_SYNTHESE_-_BTS_SIO_2026.xlsx
+++ b/documents/EPREUVE_E5_TABLEAU_DE_SYNTHESE_-_BTS_SIO_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PorteFolio\PorteFolio\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AFB0827-1262-4A29-B212-E3256110AE74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A79BF2AE-81AF-4E39-B245-328F1A2FC934}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="50">
   <si>
     <t>Gérer le patrimoine informatique</t>
   </si>
@@ -137,9 +137,6 @@
     <t>X</t>
   </si>
   <si>
-    <t xml:space="preserve">       X</t>
-  </si>
-  <si>
     <t>Sécurisation Keepass</t>
   </si>
   <si>
@@ -152,9 +149,6 @@
     <t xml:space="preserve">               X</t>
   </si>
   <si>
-    <t xml:space="preserve">              X</t>
-  </si>
-  <si>
     <t>x</t>
   </si>
   <si>
@@ -192,6 +186,12 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                 X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                X</t>
   </si>
 </sst>
 </file>
@@ -663,7 +663,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -739,15 +739,39 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -781,29 +805,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1246,56 +1249,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26" t="s">
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="26"/>
+      <c r="H1" s="24"/>
     </row>
     <row r="2" spans="1:43" ht="41.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
     </row>
     <row r="3" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="44" t="s">
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="39"/>
-      <c r="H3" s="45"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="32"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="42"/>
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="43"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="30"/>
       <c r="F4" s="12" t="s">
         <v>8</v>
       </c>
@@ -1307,22 +1310,22 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="36"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="37"/>
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="45"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="33" t="s">
+      <c r="B6" s="41" t="s">
         <v>19</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1345,8 +1348,8 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="325" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="25"/>
-      <c r="B7" s="34"/>
+      <c r="A7" s="34"/>
+      <c r="B7" s="42"/>
       <c r="C7" s="20" t="s">
         <v>9</v>
       </c>
@@ -1402,16 +1405,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="17.600000000000001" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="28"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="29"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="37"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1453,23 +1456,23 @@
         <v>28</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E9" s="14"/>
       <c r="F9" s="14" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="H9" s="14" t="s">
-        <v>37</v>
+        <v>35</v>
+      </c>
+      <c r="H9" s="46" t="s">
+        <v>30</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
@@ -1512,28 +1515,28 @@
         <v>27</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E10" s="14"/>
       <c r="F10" s="14" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="H10" s="14" t="s">
-        <v>37</v>
+        <v>35</v>
+      </c>
+      <c r="H10" s="46" t="s">
+        <v>30</v>
       </c>
       <c r="J10"/>
       <c r="K10"/>
       <c r="L10" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M10"/>
       <c r="N10"/>
@@ -1569,24 +1572,24 @@
     </row>
     <row r="11" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D11" s="14"/>
       <c r="E11" s="14"/>
       <c r="F11" s="14" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="H11" s="14" t="s">
-        <v>37</v>
+        <v>35</v>
+      </c>
+      <c r="H11" s="46" t="s">
+        <v>30</v>
       </c>
       <c r="I11"/>
       <c r="J11"/>
@@ -1626,26 +1629,26 @@
     </row>
     <row r="12" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E12" s="15"/>
       <c r="F12" s="14" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="H12" s="14" t="s">
-        <v>37</v>
+        <v>35</v>
+      </c>
+      <c r="H12" s="46" t="s">
+        <v>30</v>
       </c>
       <c r="I12"/>
       <c r="J12"/>
@@ -1685,28 +1688,28 @@
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="H13" s="14" t="s">
-        <v>37</v>
+        <v>35</v>
+      </c>
+      <c r="H13" s="46" t="s">
+        <v>30</v>
       </c>
       <c r="I13"/>
       <c r="J13"/>
@@ -1970,16 +1973,16 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="17.600000000000001" x14ac:dyDescent="0.3">
-      <c r="A19" s="30" t="s">
+      <c r="A19" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="31"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="32"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="40"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -2018,29 +2021,27 @@
     </row>
     <row r="20" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>34</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="H20" s="16"/>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
@@ -2079,28 +2080,28 @@
     </row>
     <row r="21" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="D21" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G21" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>31</v>
+      <c r="H21" s="46" t="s">
+        <v>30</v>
       </c>
       <c r="I21"/>
       <c r="J21"/>
@@ -2364,16 +2365,16 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="17.600000000000001" x14ac:dyDescent="0.3">
-      <c r="A27" s="30" t="s">
+      <c r="A27" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="B27" s="31"/>
-      <c r="C27" s="31"/>
-      <c r="D27" s="31"/>
-      <c r="E27" s="31"/>
-      <c r="F27" s="31"/>
-      <c r="G27" s="31"/>
-      <c r="H27" s="32"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="39"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="39"/>
+      <c r="G27" s="39"/>
+      <c r="H27" s="40"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2415,13 +2416,13 @@
         <v>29</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E28" s="21"/>
       <c r="F28" s="21" t="s">
@@ -2832,11 +2833,6 @@
     <row r="81" customFormat="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2844,6 +2840,11 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/documents/EPREUVE_E5_TABLEAU_DE_SYNTHESE_-_BTS_SIO_2026.xlsx
+++ b/documents/EPREUVE_E5_TABLEAU_DE_SYNTHESE_-_BTS_SIO_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PorteFolio\PorteFolio\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A79BF2AE-81AF-4E39-B245-328F1A2FC934}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63AE6AE6-0A75-4B3F-8011-2AFAF1131273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="51">
   <si>
     <t>Gérer le patrimoine informatique</t>
   </si>
@@ -192,6 +192,9 @@
   </si>
   <si>
     <t xml:space="preserve">                X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                </t>
   </si>
 </sst>
 </file>
@@ -739,9 +742,51 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -765,48 +810,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1239,66 +1242,66 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AQ81"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.84375" defaultRowHeight="12.45" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="70.3828125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="37.15234375" style="1" customWidth="1"/>
-    <col min="3" max="8" width="18.69140625" style="1" customWidth="1"/>
-    <col min="9" max="43" width="11.3828125" customWidth="1"/>
-    <col min="44" max="16384" width="10.84375" style="1"/>
+    <col min="1" max="1" width="70.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="37.140625" style="1" customWidth="1"/>
+    <col min="3" max="8" width="18.7109375" style="1" customWidth="1"/>
+    <col min="9" max="43" width="11.42578125" customWidth="1"/>
+    <col min="44" max="16384" width="10.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24" t="s">
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="24"/>
-    </row>
-    <row r="2" spans="1:43" ht="41.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="24" t="s">
+      <c r="H1" s="27"/>
+    </row>
+    <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-    </row>
-    <row r="3" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="25" t="s">
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+    </row>
+    <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="31" t="s">
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="26"/>
-      <c r="H3" s="32"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="46"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="28" t="s">
+    <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="30"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="44"/>
       <c r="F4" s="12" t="s">
         <v>8</v>
       </c>
@@ -1309,23 +1312,23 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:43" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="43" t="s">
+    <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="45"/>
-    </row>
-    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="33" t="s">
+      <c r="B5" s="37"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="38"/>
+    </row>
+    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="41" t="s">
+      <c r="B6" s="34" t="s">
         <v>19</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1347,9 +1350,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:43" s="2" customFormat="1" ht="325" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="34"/>
-      <c r="B7" s="42"/>
+    <row r="7" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="26"/>
+      <c r="B7" s="35"/>
       <c r="C7" s="20" t="s">
         <v>9</v>
       </c>
@@ -1404,17 +1407,17 @@
       <c r="AP7"/>
       <c r="AQ7"/>
     </row>
-    <row r="8" spans="1:43" s="2" customFormat="1" ht="17.600000000000001" x14ac:dyDescent="0.3">
-      <c r="A8" s="35" t="s">
+    <row r="8" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+      <c r="A8" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="36"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="37"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="30"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1451,7 +1454,7 @@
       <c r="AP8"/>
       <c r="AQ8"/>
     </row>
-    <row r="9" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
         <v>28</v>
       </c>
@@ -1471,7 +1474,7 @@
       <c r="G9" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="H9" s="46" t="s">
+      <c r="H9" s="24" t="s">
         <v>30</v>
       </c>
       <c r="I9"/>
@@ -1510,7 +1513,7 @@
       <c r="AP9"/>
       <c r="AQ9"/>
     </row>
-    <row r="10" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
         <v>27</v>
       </c>
@@ -1530,7 +1533,7 @@
       <c r="G10" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="H10" s="46" t="s">
+      <c r="H10" s="24" t="s">
         <v>30</v>
       </c>
       <c r="J10"/>
@@ -1570,7 +1573,7 @@
       <c r="AP10"/>
       <c r="AQ10"/>
     </row>
-    <row r="11" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
         <v>38</v>
       </c>
@@ -1588,7 +1591,7 @@
       <c r="G11" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="H11" s="46" t="s">
+      <c r="H11" s="24" t="s">
         <v>30</v>
       </c>
       <c r="I11"/>
@@ -1627,7 +1630,7 @@
       <c r="AP11"/>
       <c r="AQ11"/>
     </row>
-    <row r="12" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
         <v>36</v>
       </c>
@@ -1647,7 +1650,7 @@
       <c r="G12" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="H12" s="46" t="s">
+      <c r="H12" s="24" t="s">
         <v>30</v>
       </c>
       <c r="I12"/>
@@ -1686,7 +1689,7 @@
       <c r="AP12"/>
       <c r="AQ12"/>
     </row>
-    <row r="13" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
         <v>37</v>
       </c>
@@ -1708,7 +1711,7 @@
       <c r="G13" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="H13" s="46" t="s">
+      <c r="H13" s="24" t="s">
         <v>30</v>
       </c>
       <c r="I13"/>
@@ -1747,7 +1750,7 @@
       <c r="AP13"/>
       <c r="AQ13"/>
     </row>
-    <row r="14" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="9"/>
       <c r="B14" s="8"/>
       <c r="C14" s="15"/>
@@ -1792,7 +1795,7 @@
       <c r="AP14"/>
       <c r="AQ14"/>
     </row>
-    <row r="15" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="9"/>
       <c r="B15" s="8"/>
       <c r="C15" s="15"/>
@@ -1837,7 +1840,7 @@
       <c r="AP15"/>
       <c r="AQ15"/>
     </row>
-    <row r="16" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="9"/>
       <c r="B16" s="8"/>
       <c r="C16" s="15"/>
@@ -1882,7 +1885,7 @@
       <c r="AP16"/>
       <c r="AQ16"/>
     </row>
-    <row r="17" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="9"/>
       <c r="B17" s="8"/>
       <c r="C17" s="15"/>
@@ -1927,7 +1930,7 @@
       <c r="AP17"/>
       <c r="AQ17"/>
     </row>
-    <row r="18" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="9"/>
       <c r="B18" s="8"/>
       <c r="C18" s="15"/>
@@ -1972,17 +1975,17 @@
       <c r="AP18"/>
       <c r="AQ18"/>
     </row>
-    <row r="19" spans="1:43" s="2" customFormat="1" ht="17.600000000000001" x14ac:dyDescent="0.3">
-      <c r="A19" s="38" t="s">
+    <row r="19" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+      <c r="A19" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="39"/>
-      <c r="C19" s="39"/>
-      <c r="D19" s="39"/>
-      <c r="E19" s="39"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="39"/>
-      <c r="H19" s="40"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="33"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -2019,7 +2022,7 @@
       <c r="AP19"/>
       <c r="AQ19"/>
     </row>
-    <row r="20" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
         <v>31</v>
       </c>
@@ -2036,7 +2039,7 @@
         <v>33</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G20" s="8" t="s">
         <v>48</v>
@@ -2078,7 +2081,7 @@
       <c r="AP20"/>
       <c r="AQ20"/>
     </row>
-    <row r="21" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
         <v>32</v>
       </c>
@@ -2089,7 +2092,7 @@
         <v>33</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="E21" s="8" t="s">
         <v>33</v>
@@ -2100,7 +2103,7 @@
       <c r="G21" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="H21" s="46" t="s">
+      <c r="H21" s="24" t="s">
         <v>30</v>
       </c>
       <c r="I21"/>
@@ -2139,7 +2142,7 @@
       <c r="AP21"/>
       <c r="AQ21"/>
     </row>
-    <row r="22" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="9"/>
       <c r="B22" s="8"/>
       <c r="C22" s="15"/>
@@ -2184,7 +2187,7 @@
       <c r="AP22"/>
       <c r="AQ22"/>
     </row>
-    <row r="23" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="9"/>
       <c r="B23" s="8"/>
       <c r="C23" s="15"/>
@@ -2229,7 +2232,7 @@
       <c r="AP23"/>
       <c r="AQ23"/>
     </row>
-    <row r="24" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="9"/>
       <c r="B24" s="8"/>
       <c r="C24" s="15"/>
@@ -2274,7 +2277,7 @@
       <c r="AP24"/>
       <c r="AQ24"/>
     </row>
-    <row r="25" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="9"/>
       <c r="B25" s="8"/>
       <c r="C25" s="15"/>
@@ -2319,7 +2322,7 @@
       <c r="AP25"/>
       <c r="AQ25"/>
     </row>
-    <row r="26" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="9"/>
       <c r="B26" s="8"/>
       <c r="C26" s="15"/>
@@ -2364,17 +2367,17 @@
       <c r="AP26"/>
       <c r="AQ26"/>
     </row>
-    <row r="27" spans="1:43" s="2" customFormat="1" ht="17.600000000000001" x14ac:dyDescent="0.3">
-      <c r="A27" s="38" t="s">
+    <row r="27" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+      <c r="A27" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="B27" s="39"/>
-      <c r="C27" s="39"/>
-      <c r="D27" s="39"/>
-      <c r="E27" s="39"/>
-      <c r="F27" s="39"/>
-      <c r="G27" s="39"/>
-      <c r="H27" s="40"/>
+      <c r="B27" s="32"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="33"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2411,7 +2414,7 @@
       <c r="AP27"/>
       <c r="AQ27"/>
     </row>
-    <row r="28" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
         <v>29</v>
       </c>
@@ -2470,7 +2473,7 @@
       <c r="AP28"/>
       <c r="AQ28"/>
     </row>
-    <row r="29" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="9"/>
       <c r="B29" s="8"/>
       <c r="C29" s="15"/>
@@ -2515,7 +2518,7 @@
       <c r="AP29"/>
       <c r="AQ29"/>
     </row>
-    <row r="30" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="9"/>
       <c r="B30" s="8"/>
       <c r="C30" s="15"/>
@@ -2560,7 +2563,7 @@
       <c r="AP30"/>
       <c r="AQ30"/>
     </row>
-    <row r="31" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="9"/>
       <c r="B31" s="8"/>
       <c r="C31" s="15"/>
@@ -2605,7 +2608,7 @@
       <c r="AP31"/>
       <c r="AQ31"/>
     </row>
-    <row r="32" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="9"/>
       <c r="B32" s="8"/>
       <c r="C32" s="15"/>
@@ -2650,7 +2653,7 @@
       <c r="AP32"/>
       <c r="AQ32"/>
     </row>
-    <row r="33" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="9"/>
       <c r="B33" s="8"/>
       <c r="C33" s="15"/>
@@ -2695,7 +2698,7 @@
       <c r="AP33"/>
       <c r="AQ33"/>
     </row>
-    <row r="34" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="10"/>
       <c r="B34" s="11"/>
       <c r="C34" s="17"/>
@@ -2740,7 +2743,7 @@
       <c r="AP34"/>
       <c r="AQ34"/>
     </row>
-    <row r="35" spans="1:43" s="2" customFormat="1" ht="14.15" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:43" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A35" s="5"/>
       <c r="B35" s="3"/>
       <c r="C35" s="4"/>
@@ -2785,54 +2788,59 @@
       <c r="AP35"/>
       <c r="AQ35"/>
     </row>
-    <row r="36" spans="1:43" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="37" spans="1:43" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="38" spans="1:43" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="39" spans="1:43" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="40" spans="1:43" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="41" spans="1:43" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="42" spans="1:43" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="43" spans="1:43" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="44" spans="1:43" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="45" spans="1:43" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="46" spans="1:43" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="47" spans="1:43" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="48" spans="1:43" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="49" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="50" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="51" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="52" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="53" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="54" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="55" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="56" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="57" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="58" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="59" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="60" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="61" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="62" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="63" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="64" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="65" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="66" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="67" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="68" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="69" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="70" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="71" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="72" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="73" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="74" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="75" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="76" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="77" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="78" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="79" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="80" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="81" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="36" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="37" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="38" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="39" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="40" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="41" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="42" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="43" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="44" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="45" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="46" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="47" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="48" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="49" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="50" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="51" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="52" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="54" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="55" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="56" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="57" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="58" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="59" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="60" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="61" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="62" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="63" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="64" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="65" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="66" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="68" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="69" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="70" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="71" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="72" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="73" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="74" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="75" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="76" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="77" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="78" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="79" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="80" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="81" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2840,11 +2848,6 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/documents/EPREUVE_E5_TABLEAU_DE_SYNTHESE_-_BTS_SIO_2026.xlsx
+++ b/documents/EPREUVE_E5_TABLEAU_DE_SYNTHESE_-_BTS_SIO_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PorteFolio\PorteFolio\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63AE6AE6-0A75-4B3F-8011-2AFAF1131273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F591238F-BB85-4EED-8D87-AA73DE51B9B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9" yWindow="9" windowWidth="21925" windowHeight="12977" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E5" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="50">
   <si>
     <t>Gérer le patrimoine informatique</t>
   </si>
@@ -186,9 +186,6 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t xml:space="preserve">                 X</t>
   </si>
   <si>
     <t xml:space="preserve">                X</t>
@@ -745,15 +742,39 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -785,30 +806,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1242,66 +1239,66 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AQ81"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.84375" defaultRowHeight="12.45" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="70.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="37.140625" style="1" customWidth="1"/>
-    <col min="3" max="8" width="18.7109375" style="1" customWidth="1"/>
-    <col min="9" max="43" width="11.42578125" customWidth="1"/>
-    <col min="44" max="16384" width="10.85546875" style="1"/>
+    <col min="1" max="1" width="70.3828125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="37.15234375" style="1" customWidth="1"/>
+    <col min="3" max="8" width="18.69140625" style="1" customWidth="1"/>
+    <col min="9" max="43" width="11.3828125" customWidth="1"/>
+    <col min="44" max="16384" width="10.84375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="27" t="s">
+    <row r="1" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27" t="s">
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="27"/>
-    </row>
-    <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
+      <c r="H1" s="25"/>
+    </row>
+    <row r="2" spans="1:43" ht="41.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-    </row>
-    <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="39" t="s">
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+    </row>
+    <row r="3" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="45" t="s">
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="40"/>
-      <c r="H3" s="46"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="33"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="42" t="s">
+    <row r="4" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="44"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="31"/>
       <c r="F4" s="12" t="s">
         <v>8</v>
       </c>
@@ -1312,23 +1309,23 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="36" t="s">
+    <row r="5" spans="1:43" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="38"/>
-    </row>
-    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="25" t="s">
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="46"/>
+    </row>
+    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="42" t="s">
         <v>19</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1350,9 +1347,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="26"/>
-      <c r="B7" s="35"/>
+    <row r="7" spans="1:43" s="2" customFormat="1" ht="325" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="35"/>
+      <c r="B7" s="43"/>
       <c r="C7" s="20" t="s">
         <v>9</v>
       </c>
@@ -1407,17 +1404,17 @@
       <c r="AP7"/>
       <c r="AQ7"/>
     </row>
-    <row r="8" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A8" s="28" t="s">
+    <row r="8" spans="1:43" s="2" customFormat="1" ht="17.600000000000001" x14ac:dyDescent="0.3">
+      <c r="A8" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="29"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="30"/>
+      <c r="B8" s="37"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="38"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1454,7 +1451,7 @@
       <c r="AP8"/>
       <c r="AQ8"/>
     </row>
-    <row r="9" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
         <v>28</v>
       </c>
@@ -1513,7 +1510,7 @@
       <c r="AP9"/>
       <c r="AQ9"/>
     </row>
-    <row r="10" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>27</v>
       </c>
@@ -1573,7 +1570,7 @@
       <c r="AP10"/>
       <c r="AQ10"/>
     </row>
-    <row r="11" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
         <v>38</v>
       </c>
@@ -1630,7 +1627,7 @@
       <c r="AP11"/>
       <c r="AQ11"/>
     </row>
-    <row r="12" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>36</v>
       </c>
@@ -1689,7 +1686,7 @@
       <c r="AP12"/>
       <c r="AQ12"/>
     </row>
-    <row r="13" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
         <v>37</v>
       </c>
@@ -1750,7 +1747,7 @@
       <c r="AP13"/>
       <c r="AQ13"/>
     </row>
-    <row r="14" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9"/>
       <c r="B14" s="8"/>
       <c r="C14" s="15"/>
@@ -1795,7 +1792,7 @@
       <c r="AP14"/>
       <c r="AQ14"/>
     </row>
-    <row r="15" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="9"/>
       <c r="B15" s="8"/>
       <c r="C15" s="15"/>
@@ -1840,7 +1837,7 @@
       <c r="AP15"/>
       <c r="AQ15"/>
     </row>
-    <row r="16" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="9"/>
       <c r="B16" s="8"/>
       <c r="C16" s="15"/>
@@ -1885,7 +1882,7 @@
       <c r="AP16"/>
       <c r="AQ16"/>
     </row>
-    <row r="17" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="9"/>
       <c r="B17" s="8"/>
       <c r="C17" s="15"/>
@@ -1930,7 +1927,7 @@
       <c r="AP17"/>
       <c r="AQ17"/>
     </row>
-    <row r="18" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="9"/>
       <c r="B18" s="8"/>
       <c r="C18" s="15"/>
@@ -1975,17 +1972,17 @@
       <c r="AP18"/>
       <c r="AQ18"/>
     </row>
-    <row r="19" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A19" s="31" t="s">
+    <row r="19" spans="1:43" s="2" customFormat="1" ht="17.600000000000001" x14ac:dyDescent="0.3">
+      <c r="A19" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="32"/>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="33"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="41"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -2022,7 +2019,7 @@
       <c r="AP19"/>
       <c r="AQ19"/>
     </row>
-    <row r="20" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>31</v>
       </c>
@@ -2030,20 +2027,18 @@
         <v>42</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E20" s="8" t="s">
         <v>33</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>48</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="G20" s="8"/>
       <c r="H20" s="16"/>
       <c r="I20"/>
       <c r="J20"/>
@@ -2081,7 +2076,7 @@
       <c r="AP20"/>
       <c r="AQ20"/>
     </row>
-    <row r="21" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
         <v>32</v>
       </c>
@@ -2092,17 +2087,15 @@
         <v>33</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E21" s="8" t="s">
         <v>33</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="G21" s="8" t="s">
         <v>48</v>
       </c>
+      <c r="G21" s="8"/>
       <c r="H21" s="24" t="s">
         <v>30</v>
       </c>
@@ -2142,7 +2135,7 @@
       <c r="AP21"/>
       <c r="AQ21"/>
     </row>
-    <row r="22" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="9"/>
       <c r="B22" s="8"/>
       <c r="C22" s="15"/>
@@ -2187,7 +2180,7 @@
       <c r="AP22"/>
       <c r="AQ22"/>
     </row>
-    <row r="23" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="9"/>
       <c r="B23" s="8"/>
       <c r="C23" s="15"/>
@@ -2232,7 +2225,7 @@
       <c r="AP23"/>
       <c r="AQ23"/>
     </row>
-    <row r="24" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="9"/>
       <c r="B24" s="8"/>
       <c r="C24" s="15"/>
@@ -2277,7 +2270,7 @@
       <c r="AP24"/>
       <c r="AQ24"/>
     </row>
-    <row r="25" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="9"/>
       <c r="B25" s="8"/>
       <c r="C25" s="15"/>
@@ -2322,7 +2315,7 @@
       <c r="AP25"/>
       <c r="AQ25"/>
     </row>
-    <row r="26" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="9"/>
       <c r="B26" s="8"/>
       <c r="C26" s="15"/>
@@ -2367,17 +2360,17 @@
       <c r="AP26"/>
       <c r="AQ26"/>
     </row>
-    <row r="27" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A27" s="31" t="s">
+    <row r="27" spans="1:43" s="2" customFormat="1" ht="17.600000000000001" x14ac:dyDescent="0.3">
+      <c r="A27" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="B27" s="32"/>
-      <c r="C27" s="32"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="33"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="41"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2414,7 +2407,7 @@
       <c r="AP27"/>
       <c r="AQ27"/>
     </row>
-    <row r="28" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>29</v>
       </c>
@@ -2431,9 +2424,7 @@
       <c r="F28" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="G28" s="21" t="s">
-        <v>30</v>
-      </c>
+      <c r="G28" s="21"/>
       <c r="H28" s="21" t="s">
         <v>30</v>
       </c>
@@ -2473,7 +2464,7 @@
       <c r="AP28"/>
       <c r="AQ28"/>
     </row>
-    <row r="29" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="9"/>
       <c r="B29" s="8"/>
       <c r="C29" s="15"/>
@@ -2518,7 +2509,7 @@
       <c r="AP29"/>
       <c r="AQ29"/>
     </row>
-    <row r="30" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="9"/>
       <c r="B30" s="8"/>
       <c r="C30" s="15"/>
@@ -2563,7 +2554,7 @@
       <c r="AP30"/>
       <c r="AQ30"/>
     </row>
-    <row r="31" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="9"/>
       <c r="B31" s="8"/>
       <c r="C31" s="15"/>
@@ -2608,7 +2599,7 @@
       <c r="AP31"/>
       <c r="AQ31"/>
     </row>
-    <row r="32" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="9"/>
       <c r="B32" s="8"/>
       <c r="C32" s="15"/>
@@ -2653,7 +2644,7 @@
       <c r="AP32"/>
       <c r="AQ32"/>
     </row>
-    <row r="33" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="9"/>
       <c r="B33" s="8"/>
       <c r="C33" s="15"/>
@@ -2698,7 +2689,7 @@
       <c r="AP33"/>
       <c r="AQ33"/>
     </row>
-    <row r="34" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="10"/>
       <c r="B34" s="11"/>
       <c r="C34" s="17"/>
@@ -2743,7 +2734,7 @@
       <c r="AP34"/>
       <c r="AQ34"/>
     </row>
-    <row r="35" spans="1:43" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:43" s="2" customFormat="1" ht="14.15" x14ac:dyDescent="0.3">
       <c r="A35" s="5"/>
       <c r="B35" s="3"/>
       <c r="C35" s="4"/>
@@ -2788,59 +2779,54 @@
       <c r="AP35"/>
       <c r="AQ35"/>
     </row>
-    <row r="36" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="37" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="38" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="39" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="40" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="41" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="42" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="43" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="44" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="45" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="46" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="47" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="48" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="49" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="50" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="51" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="52" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="53" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="54" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="55" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="56" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="58" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="60" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="61" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="62" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="63" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="64" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="65" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="66" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="67" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="68" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="69" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="70" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="71" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="72" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="73" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="74" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="75" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="76" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="77" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="78" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="79" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="80" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="81" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="36" spans="1:43" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="37" spans="1:43" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="38" spans="1:43" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="39" spans="1:43" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="40" spans="1:43" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="41" spans="1:43" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="42" spans="1:43" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="43" spans="1:43" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="44" spans="1:43" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="45" spans="1:43" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="46" spans="1:43" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="47" spans="1:43" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="48" spans="1:43" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="49" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="50" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="51" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="52" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="53" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="54" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="55" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="56" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="57" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="58" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="59" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="60" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="61" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="62" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="63" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="64" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="65" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="66" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="67" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="68" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="69" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="70" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="71" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="72" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="73" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="74" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="75" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="76" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="77" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="78" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="79" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="80" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="81" customFormat="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2848,6 +2834,11 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/documents/EPREUVE_E5_TABLEAU_DE_SYNTHESE_-_BTS_SIO_2026.xlsx
+++ b/documents/EPREUVE_E5_TABLEAU_DE_SYNTHESE_-_BTS_SIO_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PorteFolio\PorteFolio\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F591238F-BB85-4EED-8D87-AA73DE51B9B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E3EFEEB-BAE4-46BC-9673-6C1559A2F5B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9" yWindow="9" windowWidth="21925" windowHeight="12977" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="50">
   <si>
     <t>Gérer le patrimoine informatique</t>
   </si>
@@ -742,9 +742,48 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -767,45 +806,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1249,56 +1249,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25" t="s">
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="25"/>
+      <c r="H1" s="27"/>
     </row>
     <row r="2" spans="1:43" ht="41.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
     </row>
     <row r="3" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="32" t="s">
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="27"/>
-      <c r="H3" s="33"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="46"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="31"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="44"/>
       <c r="F4" s="12" t="s">
         <v>8</v>
       </c>
@@ -1310,22 +1310,22 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="44" t="s">
+      <c r="A5" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="45"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="46"/>
+      <c r="B5" s="37"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="38"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="34" t="s">
         <v>19</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1348,8 +1348,8 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="325" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="35"/>
-      <c r="B7" s="43"/>
+      <c r="A7" s="26"/>
+      <c r="B7" s="35"/>
       <c r="C7" s="20" t="s">
         <v>9</v>
       </c>
@@ -1405,16 +1405,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="17.600000000000001" x14ac:dyDescent="0.3">
-      <c r="A8" s="36" t="s">
+      <c r="A8" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="37"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="38"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="30"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1973,16 +1973,16 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="17.600000000000001" x14ac:dyDescent="0.3">
-      <c r="A19" s="39" t="s">
+      <c r="A19" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="40"/>
-      <c r="C19" s="40"/>
-      <c r="D19" s="40"/>
-      <c r="E19" s="40"/>
-      <c r="F19" s="40"/>
-      <c r="G19" s="40"/>
-      <c r="H19" s="41"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="33"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -2039,7 +2039,9 @@
         <v>49</v>
       </c>
       <c r="G20" s="8"/>
-      <c r="H20" s="16"/>
+      <c r="H20" s="24" t="s">
+        <v>30</v>
+      </c>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
@@ -2361,16 +2363,16 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="17.600000000000001" x14ac:dyDescent="0.3">
-      <c r="A27" s="39" t="s">
+      <c r="A27" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="B27" s="40"/>
-      <c r="C27" s="40"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="40"/>
-      <c r="F27" s="40"/>
-      <c r="G27" s="40"/>
-      <c r="H27" s="41"/>
+      <c r="B27" s="32"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="33"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2827,6 +2829,11 @@
     <row r="81" customFormat="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2834,11 +2841,6 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/documents/EPREUVE_E5_TABLEAU_DE_SYNTHESE_-_BTS_SIO_2026.xlsx
+++ b/documents/EPREUVE_E5_TABLEAU_DE_SYNTHESE_-_BTS_SIO_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PorteFolio\PorteFolio\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E3EFEEB-BAE4-46BC-9673-6C1559A2F5B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{415B9FEC-6D1B-434B-839A-CADEC0737E32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9" yWindow="9" windowWidth="21925" windowHeight="12977" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -742,15 +742,39 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -782,30 +806,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1249,56 +1249,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27" t="s">
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="27"/>
+      <c r="H1" s="25"/>
     </row>
     <row r="2" spans="1:43" ht="41.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
     </row>
     <row r="3" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="45" t="s">
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="40"/>
-      <c r="H3" s="46"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="33"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="42" t="s">
+      <c r="A4" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="44"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="31"/>
       <c r="F4" s="12" t="s">
         <v>8</v>
       </c>
@@ -1310,22 +1310,22 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="38"/>
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="46"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="42" t="s">
         <v>19</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1348,8 +1348,8 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="325" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="26"/>
-      <c r="B7" s="35"/>
+      <c r="A7" s="35"/>
+      <c r="B7" s="43"/>
       <c r="C7" s="20" t="s">
         <v>9</v>
       </c>
@@ -1405,16 +1405,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="17.600000000000001" x14ac:dyDescent="0.3">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="29"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="30"/>
+      <c r="B8" s="37"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="38"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1973,16 +1973,16 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="17.600000000000001" x14ac:dyDescent="0.3">
-      <c r="A19" s="31" t="s">
+      <c r="A19" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="32"/>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="33"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="41"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -2086,7 +2086,7 @@
         <v>46</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>48</v>
@@ -2363,16 +2363,16 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="17.600000000000001" x14ac:dyDescent="0.3">
-      <c r="A27" s="31" t="s">
+      <c r="A27" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="B27" s="32"/>
-      <c r="C27" s="32"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="33"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="41"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2829,11 +2829,6 @@
     <row r="81" customFormat="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2841,6 +2836,11 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
